--- a/sim/resources/sample/VisitorStar.xlsx
+++ b/sim/resources/sample/VisitorStar.xlsx
@@ -50,7 +50,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-百分比</t>
+百分比
+只针对有奖励的服务能力</t>
         </r>
       </text>
     </comment>
@@ -72,7 +73,10 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-概率_道具ID_数量</t>
+不同的星级影响特殊材料掉落的概率；
+万分比；
+这边空值时，直接读取等级表的概率；
+这边填值后，直接读取这边配置的概率</t>
         </r>
       </text>
     </comment>
@@ -81,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>ID</t>
   </si>
@@ -115,19 +119,13 @@
     <t>升星所需碎片</t>
   </si>
   <si>
-    <t>基础停留时长加成系数</t>
+    <t>服务能力加成系数</t>
   </si>
   <si>
-    <t>额外材料掉落</t>
-  </si>
-  <si>
-    <t>备注</t>
+    <t>概率</t>
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>list&lt;list&lt;int&gt;{_}&gt;{|}</t>
   </si>
   <si>
     <t>id</t>
@@ -145,25 +143,10 @@
     <t>Additioncoefficient</t>
   </si>
   <si>
-    <t>BonusRate</t>
+    <t>Probability</t>
   </si>
   <si>
     <t>普通路人1</t>
-  </si>
-  <si>
-    <t>0_1980000_20000</t>
-  </si>
-  <si>
-    <t>5_1980000_20000</t>
-  </si>
-  <si>
-    <t>8_1980000_20000</t>
-  </si>
-  <si>
-    <t>10_1980000_20000</t>
-  </si>
-  <si>
-    <t>15_1980000_20000</t>
   </si>
   <si>
     <t>普通路人2</t>
@@ -218,7 +201,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,12 +217,6 @@
     </font>
     <font>
       <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -752,137 +729,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -898,19 +875,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1229,19 +1197,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H131"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:G131"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
     <col min="2" max="2" width="11.625" customWidth="1"/>
     <col min="3" max="4" width="11.75" customWidth="1"/>
     <col min="5" max="5" width="15.625" customWidth="1"/>
     <col min="6" max="6" width="18.125" customWidth="1"/>
-    <col min="7" max="7" width="37.875" customWidth="1"/>
-    <col min="8" max="8" width="14.75" customWidth="1"/>
+    <col min="7" max="7" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:8">
+    <row r="1" ht="15.75" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1260,77 +1227,71 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+    </row>
+    <row r="2" ht="15.75" spans="1:7">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" ht="15.75" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" spans="1:7">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="H2" s="6"/>
-    </row>
-    <row r="3" ht="15.75" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>11</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="G3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="6"/>
-    </row>
-    <row r="4" ht="15.75" spans="1:8">
+    </row>
+    <row r="4" ht="15.75" spans="1:7">
       <c r="A4" s="1"/>
-      <c r="B4" s="7"/>
+      <c r="B4" s="4"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="6"/>
-    </row>
-    <row r="5" ht="16" customHeight="1" spans="1:8">
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" ht="16" customHeight="1" spans="1:7">
       <c r="A5" s="1">
         <f>B5*100+D5</f>
-        <v>10101</v>
+        <v>100101</v>
       </c>
       <c r="B5" s="1">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -1341,18 +1302,17 @@
       <c r="F5" s="1">
         <v>100</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="8"/>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="G5" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <f t="shared" ref="A6:A19" si="0">B6*100+D6</f>
-        <v>10102</v>
+        <v>100102</v>
       </c>
       <c r="B6" s="1">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2">
@@ -1364,18 +1324,17 @@
       <c r="F6" s="1">
         <v>150</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="8"/>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="G6" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
-        <v>10103</v>
+        <v>100103</v>
       </c>
       <c r="B7" s="1">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2">
@@ -1387,18 +1346,17 @@
       <c r="F7" s="1">
         <v>200</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="8"/>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="G7" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>10104</v>
+        <v>100104</v>
       </c>
       <c r="B8" s="1">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2">
@@ -1410,18 +1368,17 @@
       <c r="F8" s="1">
         <v>250</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="8"/>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="G8" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
-        <v>10105</v>
+        <v>100105</v>
       </c>
       <c r="B9" s="1">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2">
@@ -1433,21 +1390,20 @@
       <c r="F9" s="1">
         <v>300</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="8"/>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="G9" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>10201</v>
+        <v>100201</v>
       </c>
       <c r="B10" s="1">
-        <v>102</v>
+        <v>1002</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
@@ -1458,18 +1414,17 @@
       <c r="F10" s="1">
         <v>100</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" s="8"/>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="G10" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
-        <v>10202</v>
+        <v>100202</v>
       </c>
       <c r="B11" s="1">
-        <v>102</v>
+        <v>1002</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2">
@@ -1481,18 +1436,17 @@
       <c r="F11" s="1">
         <v>150</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="8"/>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="G11" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>10203</v>
+        <v>100203</v>
       </c>
       <c r="B12" s="1">
-        <v>102</v>
+        <v>1002</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2">
@@ -1504,18 +1458,17 @@
       <c r="F12" s="1">
         <v>200</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="8"/>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="G12" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>10204</v>
+        <v>100204</v>
       </c>
       <c r="B13" s="1">
-        <v>102</v>
+        <v>1002</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2">
@@ -1527,18 +1480,17 @@
       <c r="F13" s="1">
         <v>250</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="8"/>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="G13" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>10205</v>
+        <v>100205</v>
       </c>
       <c r="B14" s="1">
-        <v>102</v>
+        <v>1002</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2">
@@ -1550,21 +1502,20 @@
       <c r="F14" s="1">
         <v>300</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="8"/>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="G14" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
-        <v>10301</v>
+        <v>100301</v>
       </c>
       <c r="B15" s="1">
-        <v>103</v>
+        <v>1003</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -1575,18 +1526,17 @@
       <c r="F15" s="1">
         <v>100</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="8"/>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="G15" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
-        <v>10302</v>
+        <v>100302</v>
       </c>
       <c r="B16" s="1">
-        <v>103</v>
+        <v>1003</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2">
@@ -1598,18 +1548,17 @@
       <c r="F16" s="1">
         <v>150</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16" s="8"/>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="G16" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>10303</v>
+        <v>100303</v>
       </c>
       <c r="B17" s="1">
-        <v>103</v>
+        <v>1003</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2">
@@ -1621,18 +1570,17 @@
       <c r="F17" s="1">
         <v>200</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" s="8"/>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="G17" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>10304</v>
+        <v>100304</v>
       </c>
       <c r="B18" s="1">
-        <v>103</v>
+        <v>1003</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2">
@@ -1644,18 +1592,17 @@
       <c r="F18" s="1">
         <v>250</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" s="8"/>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="G18" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>10305</v>
+        <v>100305</v>
       </c>
       <c r="B19" s="1">
-        <v>103</v>
+        <v>1003</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2">
@@ -1667,21 +1614,20 @@
       <c r="F19" s="1">
         <v>300</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H19" s="8"/>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="G19" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <f t="shared" ref="A20:A51" si="1">B20*100+D20</f>
-        <v>20101</v>
+        <v>200101</v>
       </c>
       <c r="B20" s="1">
-        <v>201</v>
+        <v>2001</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D20" s="2">
         <v>1</v>
@@ -1692,18 +1638,17 @@
       <c r="F20" s="1">
         <v>100</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20" s="8"/>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="G20" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <f t="shared" si="1"/>
-        <v>20102</v>
+        <v>200102</v>
       </c>
       <c r="B21" s="1">
-        <v>201</v>
+        <v>2001</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2">
@@ -1715,18 +1660,17 @@
       <c r="F21" s="1">
         <v>150</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="8"/>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="G21" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <f t="shared" si="1"/>
-        <v>20103</v>
+        <v>200103</v>
       </c>
       <c r="B22" s="1">
-        <v>201</v>
+        <v>2001</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2">
@@ -1738,18 +1682,17 @@
       <c r="F22" s="1">
         <v>200</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H22" s="8"/>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="G22" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <f t="shared" si="1"/>
-        <v>20104</v>
+        <v>200104</v>
       </c>
       <c r="B23" s="1">
-        <v>201</v>
+        <v>2001</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2">
@@ -1761,18 +1704,17 @@
       <c r="F23" s="1">
         <v>250</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="8"/>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="G23" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <f t="shared" si="1"/>
-        <v>20105</v>
+        <v>200105</v>
       </c>
       <c r="B24" s="1">
-        <v>201</v>
+        <v>2001</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2">
@@ -1784,21 +1726,20 @@
       <c r="F24" s="1">
         <v>300</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H24" s="8"/>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="G24" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <f t="shared" si="1"/>
-        <v>20201</v>
+        <v>200201</v>
       </c>
       <c r="B25" s="1">
-        <v>202</v>
+        <v>2002</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D25" s="2">
         <v>1</v>
@@ -1809,18 +1750,17 @@
       <c r="F25" s="1">
         <v>100</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25" s="8"/>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="G25" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="1">
         <f t="shared" si="1"/>
-        <v>20202</v>
+        <v>200202</v>
       </c>
       <c r="B26" s="1">
-        <v>202</v>
+        <v>2002</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2">
@@ -1832,18 +1772,17 @@
       <c r="F26" s="1">
         <v>150</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H26" s="8"/>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="G26" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="1">
         <f t="shared" si="1"/>
-        <v>20203</v>
+        <v>200203</v>
       </c>
       <c r="B27" s="1">
-        <v>202</v>
+        <v>2002</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2">
@@ -1855,18 +1794,17 @@
       <c r="F27" s="1">
         <v>200</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H27" s="8"/>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="G27" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <f t="shared" si="1"/>
-        <v>20204</v>
+        <v>200204</v>
       </c>
       <c r="B28" s="1">
-        <v>202</v>
+        <v>2002</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2">
@@ -1878,18 +1816,17 @@
       <c r="F28" s="1">
         <v>250</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="8"/>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="G28" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="1">
         <f t="shared" si="1"/>
-        <v>20205</v>
+        <v>200205</v>
       </c>
       <c r="B29" s="1">
-        <v>202</v>
+        <v>2002</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2">
@@ -1901,21 +1838,20 @@
       <c r="F29" s="1">
         <v>300</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H29" s="8"/>
-    </row>
-    <row r="30" spans="1:8">
+      <c r="G29" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="1">
         <f t="shared" si="1"/>
-        <v>20301</v>
+        <v>200301</v>
       </c>
       <c r="B30" s="1">
-        <v>203</v>
+        <v>2003</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -1926,18 +1862,17 @@
       <c r="F30" s="1">
         <v>100</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H30" s="8"/>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="G30" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="1">
         <f t="shared" si="1"/>
-        <v>20302</v>
+        <v>200302</v>
       </c>
       <c r="B31" s="1">
-        <v>203</v>
+        <v>2003</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2">
@@ -1949,18 +1884,17 @@
       <c r="F31" s="1">
         <v>150</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H31" s="8"/>
-    </row>
-    <row r="32" spans="1:8">
+      <c r="G31" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" s="1">
         <f t="shared" si="1"/>
-        <v>20303</v>
+        <v>200303</v>
       </c>
       <c r="B32" s="1">
-        <v>203</v>
+        <v>2003</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2">
@@ -1972,18 +1906,17 @@
       <c r="F32" s="1">
         <v>200</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H32" s="8"/>
-    </row>
-    <row r="33" spans="1:8">
+      <c r="G32" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="1">
         <f t="shared" si="1"/>
-        <v>20304</v>
+        <v>200304</v>
       </c>
       <c r="B33" s="1">
-        <v>203</v>
+        <v>2003</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2">
@@ -1995,18 +1928,17 @@
       <c r="F33" s="1">
         <v>250</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="8"/>
-    </row>
-    <row r="34" spans="1:8">
+      <c r="G33" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" s="1">
         <f t="shared" si="1"/>
-        <v>20305</v>
+        <v>200305</v>
       </c>
       <c r="B34" s="1">
-        <v>203</v>
+        <v>2003</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2">
@@ -2018,21 +1950,20 @@
       <c r="F34" s="1">
         <v>300</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H34" s="8"/>
-    </row>
-    <row r="35" spans="1:8">
+      <c r="G34" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="1">
         <f t="shared" si="1"/>
-        <v>30101</v>
+        <v>300101</v>
       </c>
       <c r="B35" s="1">
-        <v>301</v>
+        <v>3001</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D35" s="2">
         <v>1</v>
@@ -2043,18 +1974,17 @@
       <c r="F35" s="1">
         <v>100</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="8"/>
-    </row>
-    <row r="36" spans="1:8">
+      <c r="G35" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" s="1">
         <f t="shared" si="1"/>
-        <v>30102</v>
+        <v>300102</v>
       </c>
       <c r="B36" s="1">
-        <v>301</v>
+        <v>3001</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2">
@@ -2066,18 +1996,17 @@
       <c r="F36" s="1">
         <v>150</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H36" s="8"/>
-    </row>
-    <row r="37" spans="1:8">
+      <c r="G36" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="1">
         <f t="shared" si="1"/>
-        <v>30103</v>
+        <v>300103</v>
       </c>
       <c r="B37" s="1">
-        <v>301</v>
+        <v>3001</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2">
@@ -2089,18 +2018,17 @@
       <c r="F37" s="1">
         <v>200</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H37" s="8"/>
-    </row>
-    <row r="38" spans="1:8">
+      <c r="G37" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" s="1">
         <f t="shared" si="1"/>
-        <v>30104</v>
+        <v>300104</v>
       </c>
       <c r="B38" s="1">
-        <v>301</v>
+        <v>3001</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2">
@@ -2112,18 +2040,17 @@
       <c r="F38" s="1">
         <v>250</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H38" s="8"/>
-    </row>
-    <row r="39" spans="1:8">
+      <c r="G38" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" s="1">
         <f t="shared" si="1"/>
-        <v>30105</v>
+        <v>300105</v>
       </c>
       <c r="B39" s="1">
-        <v>301</v>
+        <v>3001</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2">
@@ -2135,21 +2062,20 @@
       <c r="F39" s="1">
         <v>300</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="1">
+        <f t="shared" si="1"/>
+        <v>300201</v>
+      </c>
+      <c r="B40" s="1">
+        <v>3002</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="H39" s="8"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="1">
-        <f t="shared" si="1"/>
-        <v>30201</v>
-      </c>
-      <c r="B40" s="1">
-        <v>302</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="D40" s="2">
         <v>1</v>
@@ -2160,18 +2086,17 @@
       <c r="F40" s="1">
         <v>100</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H40" s="8"/>
-    </row>
-    <row r="41" spans="1:8">
+      <c r="G40" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" s="1">
         <f t="shared" si="1"/>
-        <v>30202</v>
+        <v>300202</v>
       </c>
       <c r="B41" s="1">
-        <v>302</v>
+        <v>3002</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2">
@@ -2183,18 +2108,17 @@
       <c r="F41" s="1">
         <v>150</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H41" s="8"/>
-    </row>
-    <row r="42" spans="1:8">
+      <c r="G41" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" s="1">
         <f t="shared" si="1"/>
-        <v>30203</v>
+        <v>300203</v>
       </c>
       <c r="B42" s="1">
-        <v>302</v>
+        <v>3002</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2">
@@ -2206,18 +2130,17 @@
       <c r="F42" s="1">
         <v>200</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H42" s="8"/>
-    </row>
-    <row r="43" spans="1:8">
+      <c r="G42" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" s="1">
         <f t="shared" si="1"/>
-        <v>30204</v>
+        <v>300204</v>
       </c>
       <c r="B43" s="1">
-        <v>302</v>
+        <v>3002</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2">
@@ -2229,18 +2152,17 @@
       <c r="F43" s="1">
         <v>250</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H43" s="8"/>
-    </row>
-    <row r="44" spans="1:8">
+      <c r="G43" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" s="1">
         <f t="shared" si="1"/>
-        <v>30205</v>
+        <v>300205</v>
       </c>
       <c r="B44" s="1">
-        <v>302</v>
+        <v>3002</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2">
@@ -2252,21 +2174,20 @@
       <c r="F44" s="1">
         <v>300</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H44" s="8"/>
-    </row>
-    <row r="45" spans="1:8">
+      <c r="G44" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" s="1">
         <f t="shared" si="1"/>
-        <v>30301</v>
+        <v>300301</v>
       </c>
       <c r="B45" s="1">
-        <v>303</v>
+        <v>3003</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D45" s="2">
         <v>1</v>
@@ -2277,18 +2198,17 @@
       <c r="F45" s="1">
         <v>100</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H45" s="8"/>
-    </row>
-    <row r="46" spans="1:8">
+      <c r="G45" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" s="1">
         <f t="shared" si="1"/>
-        <v>30302</v>
+        <v>300302</v>
       </c>
       <c r="B46" s="1">
-        <v>303</v>
+        <v>3003</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2">
@@ -2300,18 +2220,17 @@
       <c r="F46" s="1">
         <v>150</v>
       </c>
-      <c r="G46" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H46" s="8"/>
-    </row>
-    <row r="47" spans="1:8">
+      <c r="G46" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" s="1">
         <f t="shared" si="1"/>
-        <v>30303</v>
+        <v>300303</v>
       </c>
       <c r="B47" s="1">
-        <v>303</v>
+        <v>3003</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2">
@@ -2323,18 +2242,17 @@
       <c r="F47" s="1">
         <v>200</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H47" s="8"/>
-    </row>
-    <row r="48" spans="1:8">
+      <c r="G47" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" s="1">
         <f t="shared" si="1"/>
-        <v>30304</v>
+        <v>300304</v>
       </c>
       <c r="B48" s="1">
-        <v>303</v>
+        <v>3003</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2">
@@ -2346,18 +2264,17 @@
       <c r="F48" s="1">
         <v>250</v>
       </c>
-      <c r="G48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H48" s="8"/>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="G48" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" s="1">
         <f t="shared" si="1"/>
-        <v>30305</v>
+        <v>300305</v>
       </c>
       <c r="B49" s="1">
-        <v>303</v>
+        <v>3003</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2">
@@ -2369,21 +2286,20 @@
       <c r="F49" s="1">
         <v>300</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H49" s="8"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="G49" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" s="1">
         <f t="shared" si="1"/>
-        <v>40101</v>
+        <v>400101</v>
       </c>
       <c r="B50" s="1">
-        <v>401</v>
+        <v>4001</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D50" s="2">
         <v>1</v>
@@ -2394,18 +2310,17 @@
       <c r="F50" s="1">
         <v>100</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H50" s="8"/>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="G50" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" s="1">
         <f t="shared" si="1"/>
-        <v>40102</v>
+        <v>400102</v>
       </c>
       <c r="B51" s="1">
-        <v>401</v>
+        <v>4001</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2">
@@ -2417,18 +2332,17 @@
       <c r="F51" s="1">
         <v>150</v>
       </c>
-      <c r="G51" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H51" s="8"/>
-    </row>
-    <row r="52" spans="1:8">
+      <c r="G51" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" s="1">
         <f t="shared" ref="A52:A79" si="2">B52*100+D52</f>
-        <v>40103</v>
+        <v>400103</v>
       </c>
       <c r="B52" s="1">
-        <v>401</v>
+        <v>4001</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2">
@@ -2440,18 +2354,17 @@
       <c r="F52" s="1">
         <v>200</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H52" s="8"/>
-    </row>
-    <row r="53" spans="1:8">
+      <c r="G52" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" s="1">
         <f t="shared" si="2"/>
-        <v>40104</v>
+        <v>400104</v>
       </c>
       <c r="B53" s="1">
-        <v>401</v>
+        <v>4001</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2">
@@ -2463,18 +2376,17 @@
       <c r="F53" s="1">
         <v>250</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H53" s="8"/>
-    </row>
-    <row r="54" spans="1:8">
+      <c r="G53" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" s="1">
         <f t="shared" si="2"/>
-        <v>40105</v>
+        <v>400105</v>
       </c>
       <c r="B54" s="1">
-        <v>401</v>
+        <v>4001</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2">
@@ -2486,21 +2398,20 @@
       <c r="F54" s="1">
         <v>300</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H54" s="8"/>
-    </row>
-    <row r="55" spans="1:8">
+      <c r="G54" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" s="1">
         <f t="shared" si="2"/>
-        <v>40201</v>
+        <v>400201</v>
       </c>
       <c r="B55" s="1">
-        <v>402</v>
+        <v>4002</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D55" s="2">
         <v>1</v>
@@ -2511,18 +2422,17 @@
       <c r="F55" s="1">
         <v>100</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H55" s="8"/>
-    </row>
-    <row r="56" spans="1:8">
+      <c r="G55" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" s="1">
         <f t="shared" si="2"/>
-        <v>40202</v>
+        <v>400202</v>
       </c>
       <c r="B56" s="1">
-        <v>402</v>
+        <v>4002</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2">
@@ -2534,18 +2444,17 @@
       <c r="F56" s="1">
         <v>150</v>
       </c>
-      <c r="G56" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H56" s="8"/>
-    </row>
-    <row r="57" spans="1:8">
+      <c r="G56" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" s="1">
         <f t="shared" si="2"/>
-        <v>40203</v>
+        <v>400203</v>
       </c>
       <c r="B57" s="1">
-        <v>402</v>
+        <v>4002</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2">
@@ -2557,18 +2466,17 @@
       <c r="F57" s="1">
         <v>200</v>
       </c>
-      <c r="G57" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H57" s="8"/>
-    </row>
-    <row r="58" spans="1:8">
+      <c r="G57" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" s="1">
         <f t="shared" si="2"/>
-        <v>40204</v>
+        <v>400204</v>
       </c>
       <c r="B58" s="1">
-        <v>402</v>
+        <v>4002</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2">
@@ -2580,18 +2488,17 @@
       <c r="F58" s="1">
         <v>250</v>
       </c>
-      <c r="G58" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H58" s="8"/>
-    </row>
-    <row r="59" spans="1:8">
+      <c r="G58" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" s="1">
         <f t="shared" si="2"/>
-        <v>40205</v>
+        <v>400205</v>
       </c>
       <c r="B59" s="1">
-        <v>402</v>
+        <v>4002</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2">
@@ -2603,21 +2510,20 @@
       <c r="F59" s="1">
         <v>300</v>
       </c>
-      <c r="G59" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H59" s="8"/>
-    </row>
-    <row r="60" spans="1:8">
+      <c r="G59" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" s="1">
         <f t="shared" si="2"/>
-        <v>40301</v>
+        <v>400301</v>
       </c>
       <c r="B60" s="1">
-        <v>403</v>
+        <v>4003</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D60" s="2">
         <v>1</v>
@@ -2628,18 +2534,17 @@
       <c r="F60" s="1">
         <v>100</v>
       </c>
-      <c r="G60" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H60" s="8"/>
-    </row>
-    <row r="61" spans="1:8">
+      <c r="G60" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" s="1">
         <f t="shared" si="2"/>
-        <v>40302</v>
+        <v>400302</v>
       </c>
       <c r="B61" s="1">
-        <v>403</v>
+        <v>4003</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2">
@@ -2651,18 +2556,17 @@
       <c r="F61" s="1">
         <v>150</v>
       </c>
-      <c r="G61" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H61" s="8"/>
-    </row>
-    <row r="62" spans="1:8">
+      <c r="G61" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" s="1">
         <f t="shared" si="2"/>
-        <v>40303</v>
+        <v>400303</v>
       </c>
       <c r="B62" s="1">
-        <v>403</v>
+        <v>4003</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2">
@@ -2674,18 +2578,17 @@
       <c r="F62" s="1">
         <v>200</v>
       </c>
-      <c r="G62" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H62" s="8"/>
-    </row>
-    <row r="63" spans="1:8">
+      <c r="G62" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" s="1">
         <f t="shared" si="2"/>
-        <v>40304</v>
+        <v>400304</v>
       </c>
       <c r="B63" s="1">
-        <v>403</v>
+        <v>4003</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2">
@@ -2697,18 +2600,17 @@
       <c r="F63" s="1">
         <v>250</v>
       </c>
-      <c r="G63" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H63" s="8"/>
-    </row>
-    <row r="64" spans="1:8">
+      <c r="G63" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" s="1">
         <f t="shared" si="2"/>
-        <v>40305</v>
+        <v>400305</v>
       </c>
       <c r="B64" s="1">
-        <v>403</v>
+        <v>4003</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2">
@@ -2720,21 +2622,20 @@
       <c r="F64" s="1">
         <v>300</v>
       </c>
-      <c r="G64" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H64" s="8"/>
-    </row>
-    <row r="65" spans="1:8">
+      <c r="G64" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65" s="1">
         <f t="shared" si="2"/>
-        <v>50101</v>
+        <v>500101</v>
       </c>
       <c r="B65" s="1">
-        <v>501</v>
+        <v>5001</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D65" s="2">
         <v>1</v>
@@ -2745,18 +2646,17 @@
       <c r="F65" s="1">
         <v>100</v>
       </c>
-      <c r="G65" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H65" s="8"/>
-    </row>
-    <row r="66" spans="1:8">
+      <c r="G65" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66" s="1">
         <f t="shared" si="2"/>
-        <v>50102</v>
+        <v>500102</v>
       </c>
       <c r="B66" s="1">
-        <v>501</v>
+        <v>5001</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2">
@@ -2768,18 +2668,17 @@
       <c r="F66" s="1">
         <v>150</v>
       </c>
-      <c r="G66" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H66" s="8"/>
-    </row>
-    <row r="67" spans="1:8">
+      <c r="G66" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67" s="1">
         <f t="shared" si="2"/>
-        <v>50103</v>
+        <v>500103</v>
       </c>
       <c r="B67" s="1">
-        <v>501</v>
+        <v>5001</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2">
@@ -2791,18 +2690,17 @@
       <c r="F67" s="1">
         <v>200</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H67" s="8"/>
-    </row>
-    <row r="68" spans="1:8">
+      <c r="G67" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68" s="1">
         <f t="shared" si="2"/>
-        <v>50104</v>
+        <v>500104</v>
       </c>
       <c r="B68" s="1">
-        <v>501</v>
+        <v>5001</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2">
@@ -2814,18 +2712,17 @@
       <c r="F68" s="1">
         <v>250</v>
       </c>
-      <c r="G68" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H68" s="8"/>
-    </row>
-    <row r="69" spans="1:8">
+      <c r="G68" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69" s="1">
         <f t="shared" si="2"/>
-        <v>50105</v>
+        <v>500105</v>
       </c>
       <c r="B69" s="1">
-        <v>501</v>
+        <v>5001</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2">
@@ -2837,21 +2734,20 @@
       <c r="F69" s="1">
         <v>300</v>
       </c>
-      <c r="G69" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H69" s="8"/>
-    </row>
-    <row r="70" spans="1:8">
+      <c r="G69" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
       <c r="A70" s="1">
         <f t="shared" si="2"/>
-        <v>50201</v>
+        <v>500201</v>
       </c>
       <c r="B70" s="1">
-        <v>502</v>
+        <v>5002</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D70" s="2">
         <v>1</v>
@@ -2862,18 +2758,17 @@
       <c r="F70" s="1">
         <v>100</v>
       </c>
-      <c r="G70" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H70" s="8"/>
-    </row>
-    <row r="71" spans="1:8">
+      <c r="G70" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
       <c r="A71" s="1">
         <f t="shared" si="2"/>
-        <v>50202</v>
+        <v>500202</v>
       </c>
       <c r="B71" s="1">
-        <v>502</v>
+        <v>5002</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2">
@@ -2885,18 +2780,17 @@
       <c r="F71" s="1">
         <v>150</v>
       </c>
-      <c r="G71" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H71" s="8"/>
-    </row>
-    <row r="72" spans="1:8">
+      <c r="G71" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
       <c r="A72" s="1">
         <f t="shared" si="2"/>
-        <v>50203</v>
+        <v>500203</v>
       </c>
       <c r="B72" s="1">
-        <v>502</v>
+        <v>5002</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2">
@@ -2908,18 +2802,17 @@
       <c r="F72" s="1">
         <v>200</v>
       </c>
-      <c r="G72" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H72" s="8"/>
-    </row>
-    <row r="73" spans="1:8">
+      <c r="G72" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
       <c r="A73" s="1">
         <f t="shared" si="2"/>
-        <v>50204</v>
+        <v>500204</v>
       </c>
       <c r="B73" s="1">
-        <v>502</v>
+        <v>5002</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2">
@@ -2931,18 +2824,17 @@
       <c r="F73" s="1">
         <v>250</v>
       </c>
-      <c r="G73" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H73" s="8"/>
-    </row>
-    <row r="74" spans="1:8">
+      <c r="G73" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
       <c r="A74" s="1">
         <f t="shared" si="2"/>
-        <v>50205</v>
+        <v>500205</v>
       </c>
       <c r="B74" s="1">
-        <v>502</v>
+        <v>5002</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2">
@@ -2954,21 +2846,20 @@
       <c r="F74" s="1">
         <v>300</v>
       </c>
-      <c r="G74" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H74" s="8"/>
-    </row>
-    <row r="75" spans="1:8">
+      <c r="G74" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
       <c r="A75" s="1">
         <f t="shared" si="2"/>
-        <v>50301</v>
+        <v>500301</v>
       </c>
       <c r="B75" s="1">
-        <v>503</v>
+        <v>5003</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D75" s="2">
         <v>1</v>
@@ -2979,18 +2870,17 @@
       <c r="F75" s="1">
         <v>100</v>
       </c>
-      <c r="G75" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H75" s="8"/>
-    </row>
-    <row r="76" spans="1:8">
+      <c r="G75" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
       <c r="A76" s="1">
         <f t="shared" si="2"/>
-        <v>50302</v>
+        <v>500302</v>
       </c>
       <c r="B76" s="1">
-        <v>503</v>
+        <v>5003</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2">
@@ -3002,18 +2892,17 @@
       <c r="F76" s="1">
         <v>150</v>
       </c>
-      <c r="G76" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H76" s="8"/>
-    </row>
-    <row r="77" spans="1:8">
+      <c r="G76" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
       <c r="A77" s="1">
         <f t="shared" si="2"/>
-        <v>50303</v>
+        <v>500303</v>
       </c>
       <c r="B77" s="1">
-        <v>503</v>
+        <v>5003</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2">
@@ -3025,18 +2914,17 @@
       <c r="F77" s="1">
         <v>200</v>
       </c>
-      <c r="G77" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H77" s="8"/>
-    </row>
-    <row r="78" spans="1:8">
+      <c r="G77" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
       <c r="A78" s="1">
         <f t="shared" si="2"/>
-        <v>50304</v>
+        <v>500304</v>
       </c>
       <c r="B78" s="1">
-        <v>503</v>
+        <v>5003</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2">
@@ -3048,18 +2936,17 @@
       <c r="F78" s="1">
         <v>250</v>
       </c>
-      <c r="G78" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H78" s="8"/>
-    </row>
-    <row r="79" spans="1:8">
+      <c r="G78" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
       <c r="A79" s="1">
         <f t="shared" si="2"/>
-        <v>50305</v>
+        <v>500305</v>
       </c>
       <c r="B79" s="1">
-        <v>503</v>
+        <v>5003</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="2">
@@ -3071,19 +2958,18 @@
       <c r="F79" s="1">
         <v>300</v>
       </c>
-      <c r="G79" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H79" s="8"/>
+      <c r="G79" s="1">
+        <v>6000</v>
+      </c>
     </row>
     <row r="114" ht="14.25" spans="5:5">
-      <c r="E114" s="9"/>
+      <c r="E114" s="6"/>
     </row>
     <row r="130" ht="14.25" spans="5:5">
-      <c r="E130" s="9"/>
+      <c r="E130" s="6"/>
     </row>
     <row r="131" ht="14.25" spans="5:5">
-      <c r="E131" s="9"/>
+      <c r="E131" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
